--- a/import-templates/Readings and Documents import template.xlsx
+++ b/import-templates/Readings and Documents import template.xlsx
@@ -65,7 +65,23 @@
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Title</t>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="11"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">Title</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="11"/>
+              <color rgb="FFFF0000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve"> *</t>
+          </r>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
@@ -596,7 +612,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Column names must be spelled exactly as in row 1. Keep row 1 as the headers. Save/download as .xlsx. PDF files cannot come from the sheet: attach them in Payload after importing. The Keywords tab pairs each keyword with its translation. This tab is ignored by the import.</t>
+          <t xml:space="preserve">A red * marks a required column. Column names must be spelled exactly as in row 1 (the * can stay or go). Keep row 1 as the headers. Save/download as .xlsx. PDF files cannot come from the sheet: attach them in Payload after importing. The Keywords tab pairs each keyword with its translation. This tab is ignored by the import.</t>
         </is>
       </c>
     </row>

--- a/import-templates/Readings and Documents import template.xlsx
+++ b/import-templates/Readings and Documents import template.xlsx
@@ -412,7 +412,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book / Book chapter / Article / Report / Document (declarations, laws, charters, codes) / Thesis / Video (also audio) / Website. EMPTY = Article. Anything else becomes Other.</t>
+          <t xml:space="preserve">One of: Book ; Book chapter ; Article ; Report ; Document (declarations, laws, charters, codes) ; Thesis ; Video (also audio) ; Website. EMPTY = Article. Anything else becomes Other.</t>
         </is>
       </c>
     </row>

--- a/import-templates/Readings and Documents import template.xlsx
+++ b/import-templates/Readings and Documents import template.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Readings" sheetId="1" r:id="rId1"/>
-    <sheet name="Keywords" sheetId="2" r:id="rId2"/>
-    <sheet name="How to fill in" sheetId="3" r:id="rId3"/>
+    <sheet name="How to fill in" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -106,30 +105,25 @@
       </c>
       <c r="H1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Keywords</t>
+          <t xml:space="preserve">Note</t>
         </is>
       </c>
       <c r="I1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Note</t>
+          <t xml:space="preserve">Note_ar</t>
         </is>
       </c>
       <c r="J1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Note_ar</t>
+          <t xml:space="preserve">Other_title</t>
         </is>
       </c>
       <c r="K1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Other_title</t>
+          <t xml:space="preserve">Other_URL</t>
         </is>
       </c>
       <c r="L1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Other_URL</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Internal note</t>
         </is>
@@ -143,7 +137,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">en</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -173,30 +167,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human rights|Human dignity</t>
+          <t xml:space="preserve">TEST ROW. The 1948 declaration of the rights of every person.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEST ROW. The 1948 declaration of the rights of every person.</t>
+          <t xml:space="preserve">صف تجريبي. إعلان عام 1948 لحقوق كل إنسان.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">صف تجريبي. إعلان عام 1948 لحقوق كل إنسان.</t>
+          <t xml:space="preserve">الإعلان العالمي لحقوق الإنسان</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإعلان العالمي لحقوق الإنسان</t>
+          <t xml:space="preserve">https://www.un.org/ar/about-us/universal-declaration-of-human-rights</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.un.org/ar/about-us/universal-declaration-of-human-rights</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Test row -- delete after testing.</t>
         </is>
@@ -210,7 +199,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">en</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -240,58 +229,24 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research ethics|Human dignity</t>
+          <t xml:space="preserve">TEST ROW. Ethical principles for research involving human subjects.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEST ROW. Ethical principles for research involving human subjects.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Article</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">en</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Concept of Human Dignity and the Realistic Utopia of Human Rights</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jürgen Habermas</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Metaphilosophy</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2010</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Human dignity|Philosophy</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TEST ROW. On human dignity as the moral source of human rights.</t>
+          <t xml:space="preserve">صف تجريبي. المبادئ الأخلاقية للأبحاث التي تشمل البشر.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of the options in the dropdown." sqref="A2:A1048576">
+      <formula1>"Book,Book chapter,Article,Report,Document,Thesis,Video or audio,Website,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of the options in the dropdown." sqref="B2:B1048576">
+      <formula1>"English,Arabic,Other"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 
@@ -301,318 +256,108 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">English</t>
+          <t xml:space="preserve">Column</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Arabic</t>
+          <t xml:space="preserve">What to enter</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human dignity</t>
+          <t xml:space="preserve">* columns</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">الكرامة الإنسانية</t>
+          <t xml:space="preserve">Required. Leave the column names in row 1 exactly as they are.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human rights</t>
+          <t xml:space="preserve">Type, Lang</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">حقوق الإنسان</t>
+          <t xml:space="preserve">Pick from the dropdown. Document = declarations, laws, charters, codes. Type left empty = Article.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophy</t>
+          <t xml:space="preserve">Names</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفلسفة</t>
+          <t xml:space="preserve">Authors or the body that issued it. Several are separated by | e.g. Hannah Arendt|Judith Butler</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research ethics</t>
+          <t xml:space="preserve">Source</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">أخلاقيات البحث</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Column</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Required?</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">What to enter</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Title</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The only required column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One of: Book ; Book chapter ; Article ; Report ; Document (declarations, laws, charters, codes) ; Thesis ; Video (also audio) ; Website. EMPTY = Article. Anything else becomes Other.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lang</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">en or ar. Empty = guessed from the title (Arabic letters = Arabic).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Names</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Authors, separated by |</t>
+          <t xml:space="preserve">Where it is from: journal, book, website or publisher.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Source</t>
+          <t xml:space="preserve">Note / Note_ar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Where it was published: journal, book, website or publisher.</t>
+          <t xml:space="preserve">Short note in English / in Arabic, shown on the website. One alone is shown in both languages.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year</t>
+          <t xml:space="preserve">Other_title / Other_URL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">e.g. 1948</t>
+          <t xml:space="preserve">The same source in the other language, if there is one.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL</t>
+          <t xml:space="preserve">Internal note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link to the reading.</t>
+          <t xml:space="preserve">For the team only, never shown on the website.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keywords</t>
+          <t xml:space="preserve">Keywords and files</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Separated by |, e.g. Human rights|Human dignity</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Short note in English, shown on the website.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note_ar</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Short note in Arabic, shown on the website.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other_title</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Title of the same reading in the other language.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other_URL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link to that other-language version.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Internal note</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the team only, not shown on the website.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rules</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A red * marks a required column. Column names must be spelled exactly as in row 1 (the * can stay or go). Keep row 1 as the headers. Save/download as .xlsx. PDF files cannot come from the sheet: attach them in Payload after importing. The Keywords tab pairs each keyword with its translation. This tab is ignored by the import.</t>
+          <t xml:space="preserve">Not in the sheet: add them in Payload after importing.</t>
         </is>
       </c>
     </row>
